--- a/results/pooled_results_OR_unadj_and_adj_for_demog.xlsx
+++ b/results/pooled_results_OR_unadj_and_adj_for_demog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Keiji\Documents\Research\ahs_fibromyalgia\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86205D67-624A-44A9-A6FE-D735B26354CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED07DDE2-6FFF-448C-B7E9-653CE5241E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{177764AB-8017-4EAB-A19C-7FCEE5148295}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="44">
   <si>
     <t>One</t>
   </si>
@@ -193,6 +193,9 @@
   <si>
     <t>Incident FM</t>
   </si>
+  <si>
+    <t>Unknown</t>
+  </si>
 </sst>
 </file>
 
@@ -200,8 +203,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -282,31 +285,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -642,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D09C39-1F64-4281-A5B5-6E33195015DD}">
-  <dimension ref="B1:N49"/>
+  <dimension ref="B1:N50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
@@ -650,96 +656,97 @@
     <col min="4" max="8" width="7.77734375" customWidth="1"/>
     <col min="9" max="9" width="2.88671875" customWidth="1"/>
     <col min="10" max="12" width="7.77734375" style="1" customWidth="1"/>
-    <col min="13" max="14" width="7.77734375" customWidth="1"/>
+    <col min="13" max="13" width="7.77734375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="14" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="15">
         <v>3136</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="15">
         <v>136</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14" t="s">
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="6" t="s">
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="12"/>
     </row>
     <row r="7" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15" t="s">
+      <c r="I7" s="13"/>
+      <c r="J7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="15" t="s">
+      <c r="K7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="15" t="s">
+      <c r="L7" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="M7" s="15" t="s">
+      <c r="M7" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="N7" s="15" t="s">
+      <c r="N7" s="13" t="s">
         <v>30</v>
       </c>
     </row>
@@ -753,83 +760,83 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="H8" s="7">
+      <c r="E8" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="16"/>
+      <c r="H8" s="6">
         <v>5.1000000000000004E-3</v>
       </c>
       <c r="J8" s="1">
         <v>1</v>
       </c>
-      <c r="K8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="4"/>
-      <c r="N8" s="7">
-        <v>3.3E-3</v>
+      <c r="K8" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="17"/>
+      <c r="N8" s="6">
+        <v>1.37E-2</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>1.7617</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>1.2122999999999999</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>2.5602</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="6">
         <v>2.9965999999999999E-3</v>
       </c>
       <c r="H9" s="2"/>
-      <c r="J9" s="6">
-        <v>1.8354999999999999</v>
-      </c>
-      <c r="K9" s="6">
-        <v>1.2552000000000001</v>
-      </c>
-      <c r="L9" s="6">
-        <v>2.6842000000000001</v>
-      </c>
-      <c r="M9" s="7">
-        <v>1.7449E-3</v>
-      </c>
-      <c r="N9" s="7"/>
+      <c r="J9" s="5">
+        <v>1.7074</v>
+      </c>
+      <c r="K9" s="5">
+        <v>1.1605000000000001</v>
+      </c>
+      <c r="L9" s="5">
+        <v>2.5121000000000002</v>
+      </c>
+      <c r="M9" s="6">
+        <v>6.6344000000000004E-3</v>
+      </c>
+      <c r="N9" s="6"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>1.6888000000000001</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>1.0066999999999999</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>2.8332000000000002</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="6">
         <v>4.7137999999999999E-2</v>
       </c>
       <c r="H10" s="2"/>
-      <c r="J10" s="6">
-        <v>1.7524999999999999</v>
-      </c>
-      <c r="K10" s="6">
-        <v>1.0385</v>
-      </c>
-      <c r="L10" s="6">
-        <v>2.9573</v>
-      </c>
-      <c r="M10" s="7">
-        <v>3.5617999999999997E-2</v>
+      <c r="J10" s="1">
+        <v>1.6056999999999999</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0.94284000000000001</v>
+      </c>
+      <c r="L10" s="1">
+        <v>2.7347000000000001</v>
+      </c>
+      <c r="M10" s="2">
+        <v>8.1262000000000001E-2</v>
       </c>
       <c r="N10" s="2"/>
     </row>
@@ -839,7 +846,6 @@
       <c r="F11" s="1"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-      <c r="M11" s="2"/>
       <c r="N11" s="2"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
@@ -852,24 +858,23 @@
       <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="4"/>
+      <c r="E12" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="16"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="7">
+      <c r="H12" s="6">
         <v>1.4500000000000001E-2</v>
       </c>
       <c r="J12" s="1">
         <v>1</v>
       </c>
-      <c r="K12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="7">
-        <v>9.7999999999999997E-3</v>
+      <c r="K12" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="17"/>
+      <c r="N12" s="6">
+        <v>5.6599999999999998E-2</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
@@ -890,16 +895,16 @@
       </c>
       <c r="H13" s="2"/>
       <c r="J13" s="1">
-        <v>1.4227000000000001</v>
+        <v>1.2939000000000001</v>
       </c>
       <c r="K13" s="1">
-        <v>0.96587999999999996</v>
+        <v>0.87231000000000003</v>
       </c>
       <c r="L13" s="1">
-        <v>2.0956000000000001</v>
+        <v>1.9193</v>
       </c>
       <c r="M13" s="2">
-        <v>7.4366000000000002E-2</v>
+        <v>0.20016999999999999</v>
       </c>
       <c r="N13" s="2"/>
     </row>
@@ -907,30 +912,30 @@
       <c r="C14" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>1.8691</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="5">
         <v>1.0390999999999999</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
         <v>3.3620000000000001</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="6">
         <v>3.6797999999999997E-2</v>
       </c>
       <c r="H14" s="2"/>
-      <c r="J14" s="6">
-        <v>1.9598</v>
-      </c>
-      <c r="K14" s="6">
-        <v>1.0824</v>
-      </c>
-      <c r="L14" s="6">
-        <v>3.5484</v>
-      </c>
-      <c r="M14" s="7">
-        <v>2.6341E-2</v>
+      <c r="J14" s="1">
+        <v>1.6781999999999999</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0.91525999999999996</v>
+      </c>
+      <c r="L14" s="1">
+        <v>3.0771999999999999</v>
+      </c>
+      <c r="M14" s="2">
+        <v>9.4160999999999995E-2</v>
       </c>
       <c r="N14" s="2"/>
     </row>
@@ -940,7 +945,6 @@
       <c r="F15" s="1"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-      <c r="M15" s="2"/>
       <c r="N15" s="2"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
@@ -953,20 +957,19 @@
       <c r="D16" s="1">
         <v>1</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" s="4"/>
+      <c r="E16" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="16"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="J16" s="1">
         <v>1</v>
       </c>
-      <c r="K16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L16" s="4"/>
-      <c r="M16" s="2"/>
+      <c r="K16" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="17"/>
       <c r="N16" s="2"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.3">
@@ -987,16 +990,16 @@
       </c>
       <c r="H17" s="2"/>
       <c r="J17" s="1">
-        <v>1.5125</v>
+        <v>1.31</v>
       </c>
       <c r="K17" s="1">
-        <v>0.97118000000000004</v>
+        <v>0.82987999999999995</v>
       </c>
       <c r="L17" s="1">
-        <v>2.3555000000000001</v>
+        <v>2.0678000000000001</v>
       </c>
       <c r="M17" s="2">
-        <v>6.7154000000000005E-2</v>
+        <v>0.24623</v>
       </c>
       <c r="N17" s="2"/>
     </row>
@@ -1006,7 +1009,6 @@
       <c r="F18" s="1"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-      <c r="M18" s="2"/>
       <c r="N18" s="2"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.3">
@@ -1019,50 +1021,49 @@
       <c r="D19" s="1">
         <v>1</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="4"/>
+      <c r="E19" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="16"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="J19" s="1">
         <v>1</v>
       </c>
-      <c r="K19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L19" s="4"/>
-      <c r="M19" s="2"/>
+      <c r="K19" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="17"/>
       <c r="N19" s="2"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <v>1.5115000000000001</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="5">
         <v>1.0391999999999999</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="5">
         <v>2.1985000000000001</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="6">
         <v>3.0713000000000001E-2</v>
       </c>
       <c r="H20" s="2"/>
-      <c r="J20" s="6">
-        <v>1.5414000000000001</v>
-      </c>
-      <c r="K20" s="6">
-        <v>1.0566</v>
-      </c>
-      <c r="L20" s="6">
-        <v>2.2486000000000002</v>
-      </c>
-      <c r="M20" s="7">
-        <v>2.4726999999999999E-2</v>
+      <c r="J20" s="1">
+        <v>1.39</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0.95074999999999998</v>
+      </c>
+      <c r="L20" s="1">
+        <v>2.0322</v>
+      </c>
+      <c r="M20" s="2">
+        <v>8.9224999999999999E-2</v>
       </c>
       <c r="N20" s="2"/>
     </row>
@@ -1072,7 +1073,6 @@
       <c r="F21" s="1"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="M21" s="2"/>
       <c r="N21" s="2"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.3">
@@ -1085,50 +1085,49 @@
       <c r="D22" s="1">
         <v>1</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22" s="4"/>
+      <c r="E22" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="16"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="J22" s="1">
         <v>1</v>
       </c>
-      <c r="K22" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L22" s="4"/>
-      <c r="M22" s="2"/>
+      <c r="K22" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="17"/>
       <c r="N22" s="2"/>
     </row>
     <row r="23" spans="2:14" ht="16.2" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="6">
-        <v>1.9368000000000001</v>
-      </c>
-      <c r="E23" s="6">
-        <v>1.1073</v>
-      </c>
-      <c r="F23" s="6">
-        <v>3.3874</v>
-      </c>
-      <c r="G23" s="7">
-        <v>2.0534E-2</v>
+      <c r="D23" s="5">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="E23" s="5">
+        <v>1.17</v>
+      </c>
+      <c r="F23" s="5">
+        <v>3.52</v>
+      </c>
+      <c r="G23" s="6">
+        <v>1.1675E-2</v>
       </c>
       <c r="H23" s="2"/>
-      <c r="J23" s="6">
-        <v>1.8733</v>
-      </c>
-      <c r="K23" s="6">
-        <v>1.0645</v>
-      </c>
-      <c r="L23" s="6">
-        <v>3.2967</v>
-      </c>
-      <c r="M23" s="7">
-        <v>2.9544000000000001E-2</v>
+      <c r="J23" s="1">
+        <v>1.7242999999999999</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0.97123000000000004</v>
+      </c>
+      <c r="L23" s="1">
+        <v>3.0613999999999999</v>
+      </c>
+      <c r="M23" s="2">
+        <v>6.2837000000000004E-2</v>
       </c>
       <c r="N23" s="2"/>
     </row>
@@ -1137,29 +1136,29 @@
         <v>15</v>
       </c>
       <c r="D24" s="1">
-        <v>0.97496000000000005</v>
+        <v>1</v>
       </c>
       <c r="E24" s="1">
-        <v>0.50504000000000004</v>
+        <v>0.51</v>
       </c>
       <c r="F24" s="1">
-        <v>1.8821000000000001</v>
+        <v>1.94</v>
       </c>
       <c r="G24" s="2">
-        <v>0.93972999999999995</v>
+        <v>0.99926999999999999</v>
       </c>
       <c r="H24" s="2"/>
       <c r="J24" s="1">
-        <v>1.0445</v>
+        <v>1.0434000000000001</v>
       </c>
       <c r="K24" s="1">
-        <v>0.53898999999999997</v>
+        <v>0.52820999999999996</v>
       </c>
       <c r="L24" s="1">
-        <v>2.0242</v>
+        <v>2.0609999999999999</v>
       </c>
       <c r="M24" s="2">
-        <v>0.89729000000000003</v>
+        <v>0.90264999999999995</v>
       </c>
       <c r="N24" s="2"/>
     </row>
@@ -1168,612 +1167,651 @@
         <v>4</v>
       </c>
       <c r="D25" s="1">
-        <v>1.7899</v>
+        <v>1.99</v>
       </c>
       <c r="E25" s="1">
-        <v>0.70469000000000004</v>
+        <v>0.78</v>
       </c>
       <c r="F25" s="1">
-        <v>4.5464000000000002</v>
+        <v>5.08</v>
       </c>
       <c r="G25" s="2">
-        <v>0.22084000000000001</v>
+        <v>0.14942</v>
       </c>
       <c r="H25" s="2"/>
       <c r="J25" s="1">
-        <v>1.7739</v>
+        <v>1.9266000000000001</v>
       </c>
       <c r="K25" s="1">
-        <v>0.69240999999999997</v>
+        <v>0.73795999999999995</v>
       </c>
       <c r="L25" s="1">
-        <v>4.5444000000000004</v>
+        <v>5.0298999999999996</v>
       </c>
       <c r="M25" s="2">
-        <v>0.23233000000000001</v>
+        <v>0.18038000000000001</v>
       </c>
       <c r="N25" s="2"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="2"/>
+      <c r="C26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1.33</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0.23050999999999999</v>
+      </c>
       <c r="H26" s="2"/>
-      <c r="M26" s="2"/>
+      <c r="J26" s="1">
+        <v>0.70289999999999997</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0.33498</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1.4749000000000001</v>
+      </c>
+      <c r="M26" s="2">
+        <v>0.35108</v>
+      </c>
       <c r="N26" s="2"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="N27" s="2"/>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C28" s="4">
         <v>0</v>
       </c>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="8" t="s">
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="16"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="M27" s="2"/>
-      <c r="N27" s="8" t="s">
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="17"/>
+      <c r="N28" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C28" s="5">
-        <v>1</v>
-      </c>
-      <c r="D28" s="1">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C29" s="4">
+        <v>1</v>
+      </c>
+      <c r="D29" s="1">
         <v>1.1691</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E29" s="1">
         <v>0.73338999999999999</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F29" s="1">
         <v>1.8637999999999999</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G29" s="2">
         <v>0.51090000000000002</v>
       </c>
-      <c r="H28" s="2"/>
-      <c r="J28" s="1">
-        <v>1.2110000000000001</v>
-      </c>
-      <c r="K28" s="1">
-        <v>0.75604000000000005</v>
-      </c>
-      <c r="L28" s="1">
-        <v>1.9396</v>
-      </c>
-      <c r="M28" s="2">
-        <v>0.42537000000000003</v>
-      </c>
-      <c r="N28" s="2"/>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C29" s="5">
+      <c r="H29" s="2"/>
+      <c r="J29" s="1">
+        <v>1.1734</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0.73467000000000005</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1.8742000000000001</v>
+      </c>
+      <c r="M29" s="2">
+        <v>0.50295999999999996</v>
+      </c>
+      <c r="N29" s="2"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C30" s="4">
         <v>2</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D30" s="5">
         <v>1.9715</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E30" s="5">
         <v>1.2310000000000001</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F30" s="5">
         <v>3.1577000000000002</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G30" s="6">
         <v>4.7638000000000003E-3</v>
       </c>
-      <c r="H29" s="2"/>
-      <c r="J29" s="6">
-        <v>2.0701000000000001</v>
-      </c>
-      <c r="K29" s="6">
-        <v>1.2829999999999999</v>
-      </c>
-      <c r="L29" s="6">
-        <v>3.34</v>
-      </c>
-      <c r="M29" s="7">
-        <v>2.8976000000000002E-3</v>
-      </c>
-      <c r="N29" s="2"/>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C30" s="5">
+      <c r="H30" s="2"/>
+      <c r="J30" s="5">
+        <v>1.9765999999999999</v>
+      </c>
+      <c r="K30" s="5">
+        <v>1.2323999999999999</v>
+      </c>
+      <c r="L30" s="5">
+        <v>3.1701999999999999</v>
+      </c>
+      <c r="M30" s="6">
+        <v>4.7139E-3</v>
+      </c>
+      <c r="N30" s="2"/>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C31" s="4">
         <v>3</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D31" s="5">
         <v>3.1318999999999999</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E31" s="5">
         <v>1.8078000000000001</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F31" s="5">
         <v>5.4259000000000004</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="G31" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H30" s="2"/>
-      <c r="J30" s="6">
-        <v>3.3607</v>
-      </c>
-      <c r="K30" s="6">
-        <v>1.9020999999999999</v>
-      </c>
-      <c r="L30" s="6">
-        <v>5.9375</v>
-      </c>
-      <c r="M30" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N30" s="2"/>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C31" s="5"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-      <c r="M31" s="2"/>
+      <c r="J31" s="5">
+        <v>3.1274000000000002</v>
+      </c>
+      <c r="K31" s="5">
+        <v>1.7521</v>
+      </c>
+      <c r="L31" s="5">
+        <v>5.5819999999999999</v>
+      </c>
+      <c r="M31" s="6">
+        <v>1.1818E-4</v>
+      </c>
       <c r="N31" s="2"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B32" t="s">
+      <c r="C32" s="4"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="N32" s="2"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C33" s="4">
         <v>0</v>
       </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="7">
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="16"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="6">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="J32" s="1">
-        <v>1</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M32" s="2"/>
-      <c r="N32" s="7">
-        <v>1.54E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C33" s="5">
-        <v>1</v>
-      </c>
-      <c r="D33" s="1">
+      <c r="J33" s="1">
+        <v>1</v>
+      </c>
+      <c r="K33" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="17"/>
+      <c r="N33" s="6">
+        <v>2.35E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C34" s="4">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1">
         <v>1.4837</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E34" s="1">
         <v>0.99651999999999996</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F34" s="1">
         <v>2.2088999999999999</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G34" s="2">
         <v>5.2038000000000001E-2</v>
       </c>
-      <c r="H33" s="2"/>
-      <c r="J33" s="1">
-        <v>1.4298</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0.95696999999999999</v>
-      </c>
-      <c r="L33" s="1">
-        <v>2.1362000000000001</v>
-      </c>
-      <c r="M33" s="2">
-        <v>8.0916000000000002E-2</v>
-      </c>
-      <c r="N33" s="2"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C34" s="5">
+      <c r="H34" s="2"/>
+      <c r="J34" s="1">
+        <v>1.4055</v>
+      </c>
+      <c r="K34" s="1">
+        <v>0.9395</v>
+      </c>
+      <c r="L34" s="1">
+        <v>2.1027999999999998</v>
+      </c>
+      <c r="M34" s="2">
+        <v>9.7627000000000005E-2</v>
+      </c>
+      <c r="N34" s="2"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C35" s="4">
         <v>2</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D35" s="5">
         <v>2.0619000000000001</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E35" s="5">
         <v>1.2583</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F35" s="5">
         <v>3.3786999999999998</v>
       </c>
-      <c r="G34" s="7">
+      <c r="G35" s="6">
         <v>4.1110000000000001E-3</v>
       </c>
-      <c r="H34" s="2"/>
-      <c r="J34" s="6">
-        <v>1.8089</v>
-      </c>
-      <c r="K34" s="6">
-        <v>1.093</v>
-      </c>
-      <c r="L34" s="6">
-        <v>2.9937</v>
-      </c>
-      <c r="M34" s="7">
-        <v>2.1146999999999999E-2</v>
-      </c>
-      <c r="N34" s="2"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C35" s="5"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-      <c r="M35" s="2"/>
+      <c r="J35" s="5">
+        <v>1.7483</v>
+      </c>
+      <c r="K35" s="5">
+        <v>1.0507</v>
+      </c>
+      <c r="L35" s="5">
+        <v>2.9093</v>
+      </c>
+      <c r="M35" s="6">
+        <v>3.1562E-2</v>
+      </c>
       <c r="N35" s="2"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B36" t="s">
+      <c r="C36" s="4"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="N36" s="2"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C37" s="4">
         <v>0</v>
       </c>
-      <c r="D36" s="1">
-        <v>1</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="7">
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" s="16"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="6">
         <v>3.0300000000000001E-2</v>
       </c>
-      <c r="M36" s="2"/>
-      <c r="N36" s="7">
-        <v>5.1000000000000004E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C37" s="5">
-        <v>1</v>
-      </c>
-      <c r="D37" s="1">
+      <c r="J37" s="1">
+        <v>1</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="17"/>
+      <c r="N37" s="6">
+        <v>4.5999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C38" s="4">
+        <v>1</v>
+      </c>
+      <c r="D38" s="1">
         <v>1.6778</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E38" s="1">
         <v>0.96296999999999999</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F38" s="1">
         <v>2.9232999999999998</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G38" s="2">
         <v>6.7684999999999995E-2</v>
       </c>
-      <c r="H37" s="2"/>
-      <c r="J37" s="1">
-        <v>1.7274</v>
-      </c>
-      <c r="K37" s="1">
-        <v>0.9879</v>
-      </c>
-      <c r="L37" s="1">
-        <v>3.0206</v>
-      </c>
-      <c r="M37" s="2">
-        <v>5.5192999999999999E-2</v>
-      </c>
-      <c r="N37" s="2"/>
-    </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C38" s="5">
+      <c r="H38" s="2"/>
+      <c r="J38" s="1">
+        <v>1.6995</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="L38" s="1">
+        <v>2.9531999999999998</v>
+      </c>
+      <c r="M38" s="2">
+        <v>5.9949000000000002E-2</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C39" s="4">
         <v>2</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D39" s="5">
         <v>1.9494</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E39" s="5">
         <v>1.0782</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F39" s="5">
         <v>3.5243000000000002</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G39" s="6">
         <v>2.7203999999999999E-2</v>
       </c>
-      <c r="H38" s="2"/>
-      <c r="J38" s="6">
-        <v>2.1974</v>
-      </c>
-      <c r="K38" s="6">
-        <v>1.2004999999999999</v>
-      </c>
-      <c r="L38" s="6">
-        <v>4.0221</v>
-      </c>
-      <c r="M38" s="7">
-        <v>1.0758E-2</v>
-      </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C39" s="5">
+      <c r="H39" s="2"/>
+      <c r="J39" s="5">
+        <v>2.177</v>
+      </c>
+      <c r="K39" s="5">
+        <v>1.2051000000000001</v>
+      </c>
+      <c r="L39" s="5">
+        <v>3.9327999999999999</v>
+      </c>
+      <c r="M39" s="6">
+        <v>9.9576999999999999E-3</v>
+      </c>
+      <c r="N39" s="2"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C40" s="4">
         <v>3</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D40" s="1">
         <v>1.9923999999999999</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E40" s="1">
         <v>0.86819999999999997</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F40" s="1">
         <v>4.5724</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G40" s="2">
         <v>0.10378</v>
       </c>
-      <c r="H39" s="2"/>
-      <c r="J39" s="6">
-        <v>2.6063000000000001</v>
-      </c>
-      <c r="K39" s="6">
-        <v>1.1157999999999999</v>
-      </c>
-      <c r="L39" s="6">
-        <v>6.0876000000000001</v>
-      </c>
-      <c r="M39" s="7">
-        <v>2.6911999999999998E-2</v>
-      </c>
-      <c r="N39" s="2"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C40" s="5"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-      <c r="M40" s="2"/>
+      <c r="J40" s="5">
+        <v>2.7023999999999999</v>
+      </c>
+      <c r="K40" s="5">
+        <v>1.1442000000000001</v>
+      </c>
+      <c r="L40" s="5">
+        <v>6.3823999999999996</v>
+      </c>
+      <c r="M40" s="6">
+        <v>2.3407000000000001E-2</v>
+      </c>
       <c r="N40" s="2"/>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B41" t="s">
+      <c r="C41" s="4"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="N41" s="2"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D41" s="1">
-        <v>1</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F41" s="4"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2">
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" s="16"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2">
         <v>0.23880000000000001</v>
       </c>
-      <c r="J41" s="1">
-        <v>1</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L41" s="4"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2">
-        <v>0.26369999999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C42" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" s="1">
-        <v>1.0535000000000001</v>
-      </c>
-      <c r="E42" s="1">
-        <v>0.62331999999999999</v>
-      </c>
-      <c r="F42" s="1">
-        <v>1.7804</v>
-      </c>
-      <c r="G42" s="2">
-        <v>0.84572999999999998</v>
-      </c>
       <c r="J42" s="1">
-        <v>1.0720000000000001</v>
-      </c>
-      <c r="K42" s="1">
-        <v>0.63124000000000002</v>
-      </c>
-      <c r="L42" s="1">
-        <v>1.8205</v>
-      </c>
-      <c r="M42" s="2">
-        <v>0.79691000000000001</v>
+        <v>1</v>
+      </c>
+      <c r="K42" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="17"/>
+      <c r="N42" s="2">
+        <v>0.35320000000000001</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D43" s="1">
-        <v>1.3946000000000001</v>
+        <v>1.0535000000000001</v>
       </c>
       <c r="E43" s="1">
-        <v>0.85736000000000001</v>
+        <v>0.62331999999999999</v>
       </c>
       <c r="F43" s="1">
-        <v>2.2685</v>
+        <v>1.7804</v>
       </c>
       <c r="G43" s="2">
-        <v>0.18015</v>
-      </c>
-      <c r="H43" s="2"/>
+        <v>0.84572999999999998</v>
+      </c>
       <c r="J43" s="1">
-        <v>1.3553999999999999</v>
+        <v>0.99655000000000005</v>
       </c>
       <c r="K43" s="1">
-        <v>0.82747000000000004</v>
+        <v>0.57316999999999996</v>
       </c>
       <c r="L43" s="1">
-        <v>2.2202000000000002</v>
+        <v>1.7326999999999999</v>
       </c>
       <c r="M43" s="2">
-        <v>0.22697999999999999</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>0.99023000000000005</v>
+      </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D44" s="1">
-        <v>1.2437</v>
+        <v>1.3946000000000001</v>
       </c>
       <c r="E44" s="1">
-        <v>0.73933000000000004</v>
+        <v>0.85736000000000001</v>
       </c>
       <c r="F44" s="1">
-        <v>2.0920999999999998</v>
+        <v>2.2685</v>
       </c>
       <c r="G44" s="2">
-        <v>0.41103000000000001</v>
+        <v>0.18015</v>
       </c>
       <c r="H44" s="2"/>
       <c r="J44" s="1">
-        <v>1.2549999999999999</v>
+        <v>1.2718</v>
       </c>
       <c r="K44" s="1">
-        <v>0.73604000000000003</v>
+        <v>0.77325999999999995</v>
       </c>
       <c r="L44" s="1">
-        <v>2.1398000000000001</v>
+        <v>2.0916999999999999</v>
       </c>
       <c r="M44" s="2">
-        <v>0.40399000000000002</v>
+        <v>0.34347</v>
       </c>
       <c r="N44" s="2"/>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="2"/>
+      <c r="C45" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1.2437</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0.73933000000000004</v>
+      </c>
+      <c r="F45" s="1">
+        <v>2.0920999999999998</v>
+      </c>
+      <c r="G45" s="2">
+        <v>0.41103000000000001</v>
+      </c>
       <c r="H45" s="2"/>
-      <c r="M45" s="2"/>
+      <c r="J45" s="1">
+        <v>1.1917</v>
+      </c>
+      <c r="K45" s="1">
+        <v>0.68462999999999996</v>
+      </c>
+      <c r="L45" s="1">
+        <v>2.0741999999999998</v>
+      </c>
+      <c r="M45" s="2">
+        <v>0.53486</v>
+      </c>
       <c r="N45" s="2"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B46" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" s="1">
-        <v>1</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F46" s="4"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
-      <c r="J46" s="1">
-        <v>1</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L46" s="4"/>
-      <c r="M46" s="2"/>
       <c r="N46" s="2"/>
     </row>
-    <row r="47" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="9"/>
-      <c r="C47" s="9" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" s="1">
+        <v>1</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F47" s="16"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
+      <c r="K47" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="17"/>
+      <c r="N47" s="2"/>
+    </row>
+    <row r="48" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="8"/>
+      <c r="C48" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D47" s="10">
+      <c r="D48" s="9">
         <v>2.5301999999999998</v>
       </c>
-      <c r="E47" s="10">
+      <c r="E48" s="9">
         <v>1.1466000000000001</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F48" s="9">
         <v>5.5834000000000001</v>
       </c>
-      <c r="G47" s="11">
+      <c r="G48" s="10">
         <v>2.1541999999999999E-2</v>
       </c>
-      <c r="H47" s="12"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="10">
-        <v>2.4500999999999999</v>
-      </c>
-      <c r="K47" s="10">
-        <v>1.0972</v>
-      </c>
-      <c r="L47" s="10">
-        <v>5.4711999999999996</v>
-      </c>
-      <c r="M47" s="11">
-        <v>2.8804E-2</v>
-      </c>
-      <c r="N47" s="12"/>
-    </row>
-    <row r="48" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B48" t="s">
+      <c r="H48" s="11"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="18">
+        <v>2.0817999999999999</v>
+      </c>
+      <c r="K48" s="18">
+        <v>0.89409000000000005</v>
+      </c>
+      <c r="L48" s="18">
+        <v>4.8474000000000004</v>
+      </c>
+      <c r="M48" s="11">
+        <v>8.9013999999999996E-2</v>
+      </c>
+      <c r="N48" s="11"/>
+    </row>
+    <row r="49" spans="2:2" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B49" t="s">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E46:F46"/>
+  <mergeCells count="20">
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="K12:L12"/>
     <mergeCell ref="K16:L16"/>
     <mergeCell ref="K19:L19"/>
     <mergeCell ref="K22:L22"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E47:F47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
